--- a/supplementary-materials/tables/Table_S08.xlsx
+++ b/supplementary-materials/tables/Table_S08.xlsx
@@ -313,16 +313,16 @@
     <t>grass + major-road density + distance to water + elevation + annual sine + annual cosine</t>
   </si>
   <si>
-    <t>Weak calibration was retained in downstream uncertainty propagation.</t>
+    <t/>
   </si>
   <si>
     <t>tree edge + built + distance to water + elevation + annual sine + annual cosine</t>
   </si>
   <si>
-    <t>Daily detection: log recording effort + log(1 + anthropogenic-event rate) + log(1 + frog-event rate) + detection-level station intercept.</t>
-  </si>
-  <si>
-    <t>The low sturnid calibration slope is reported rather than hidden. Host-model uncertainty was propagated into Koel fitting through posterior draws.</t>
+    <t/>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
